--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1402-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1402-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{452722F6-CECA-44AE-85C1-844049650248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EF604059-0EBC-4B64-A2D7-23A5A5B77843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{907BD0B5-F0F6-4F21-9F0C-A10A730CCE49}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2A951841-7385-4CEF-A701-CC6F9BEC5801}"/>
   </bookViews>
   <sheets>
     <sheet name="1402-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1604,27 +1604,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2A93FD-6AD7-4262-A10B-7C4B88A2624F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2F22E91-166B-45E9-92A6-32086A7E9C59}">
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1658,7 +1657,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1694,7 +1693,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1746,7 +1745,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1814,7 +1813,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1886,7 +1885,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1958,7 +1957,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2030,7 +2029,7 @@
         <v>4.8099999999999996</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2102,7 +2101,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2174,7 +2173,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2246,7 +2245,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2318,7 +2317,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2390,7 +2389,7 @@
         <v>5.03</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2462,7 +2461,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2534,7 +2533,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2606,7 +2605,7 @@
         <v>5.77</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2678,7 +2677,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2750,7 +2749,7 @@
         <v>5.01</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="40">
         <v>2011</v>
       </c>
@@ -2822,7 +2821,7 @@
         <v>7.12</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2010</v>
       </c>
@@ -2894,7 +2893,7 @@
         <v>8.07</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="40">
         <v>2009</v>
       </c>
@@ -2966,7 +2965,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2008</v>
       </c>
@@ -3038,7 +3037,7 @@
         <v>5.29</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2007</v>
       </c>
@@ -3110,7 +3109,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38">
         <v>2006</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>6.37</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="40">
         <v>2005</v>
       </c>
@@ -3254,7 +3253,7 @@
         <v>7.79</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2004</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="40">
         <v>2003</v>
       </c>
@@ -3398,7 +3397,7 @@
         <v>7.57</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2002</v>
       </c>
@@ -3470,7 +3469,7 @@
         <v>9.9499999999999993</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="40">
         <v>2001</v>
       </c>
@@ -3542,7 +3541,7 @@
         <v>7.73</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2000</v>
       </c>
@@ -3614,7 +3613,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="40">
         <v>1999</v>
       </c>
@@ -3686,7 +3685,7 @@
         <v>6.91</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>1998</v>
       </c>
@@ -3758,7 +3757,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="40">
         <v>1997</v>
       </c>
@@ -3830,7 +3829,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>1996</v>
       </c>
@@ -3902,7 +3901,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="45"/>
       <c r="C34" s="19" t="s">
@@ -3930,7 +3929,7 @@
       <c r="W34" s="51"/>
       <c r="X34" s="47"/>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>1995</v>
       </c>
@@ -4002,7 +4001,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="42">
         <v>1994</v>
       </c>
@@ -4074,7 +4073,7 @@
         <v>7.2</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="44"/>
       <c r="B37" s="45"/>
       <c r="C37" s="19" t="s">
@@ -4102,7 +4101,7 @@
       <c r="W37" s="51"/>
       <c r="X37" s="47"/>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="52">
         <v>1993</v>
       </c>
@@ -4174,7 +4173,7 @@
         <v>3.79</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="54"/>
       <c r="B39" s="55"/>
       <c r="C39" s="21" t="s">
@@ -4202,7 +4201,7 @@
       <c r="W39" s="61"/>
       <c r="X39" s="57"/>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="42">
         <v>1992</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>6.88</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="44"/>
       <c r="B41" s="45"/>
       <c r="C41" s="19" t="s">
@@ -4302,7 +4301,7 @@
       <c r="W41" s="51"/>
       <c r="X41" s="47"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>1991</v>
       </c>
@@ -4374,7 +4373,7 @@
         <v>7.41</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="55"/>
       <c r="C43" s="21" t="s">
@@ -4402,7 +4401,7 @@
       <c r="W43" s="61"/>
       <c r="X43" s="57"/>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>1990</v>
       </c>
@@ -4474,7 +4473,7 @@
         <v>6.22</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44"/>
       <c r="B45" s="45"/>
       <c r="C45" s="19" t="s">
@@ -4502,7 +4501,7 @@
       <c r="W45" s="51"/>
       <c r="X45" s="47"/>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="40">
         <v>1989</v>
       </c>
@@ -4574,7 +4573,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1988</v>
       </c>
@@ -4646,7 +4645,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1987</v>
       </c>
@@ -4718,7 +4717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1986</v>
       </c>
@@ -4790,7 +4789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="40">
         <v>1985</v>
       </c>
@@ -4862,7 +4861,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1984</v>
       </c>
@@ -4934,7 +4933,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="40">
         <v>1983</v>
       </c>
@@ -5006,7 +5005,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38" t="s">
         <v>69</v>
       </c>
